--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.47154985240856</v>
+        <v>6.576626851016392</v>
       </c>
       <c r="D2" t="n">
-        <v>40.44863718351053</v>
+        <v>6.572903542320461</v>
       </c>
       <c r="E2" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F2" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.1153593781069</v>
+        <v>5.868745898942372</v>
       </c>
       <c r="D3" t="n">
-        <v>36.16534193293163</v>
+        <v>5.876868064101389</v>
       </c>
       <c r="E3" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F3" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.07476867495333</v>
+        <v>5.699649909679917</v>
       </c>
       <c r="D4" t="n">
-        <v>35.16197352561805</v>
+        <v>5.713820697912934</v>
       </c>
       <c r="E4" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F4" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.42532275877662</v>
+        <v>5.431614948301202</v>
       </c>
       <c r="D5" t="n">
-        <v>33.54906413910859</v>
+        <v>5.451722922605147</v>
       </c>
       <c r="E5" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F5" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.96842807301536</v>
+        <v>5.519869561864996</v>
       </c>
       <c r="D6" t="n">
-        <v>34.10620874236991</v>
+        <v>5.542258920635111</v>
       </c>
       <c r="E6" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F6" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.92265950990905</v>
+        <v>5.512432170360221</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07092381176049</v>
+        <v>5.53652511941108</v>
       </c>
       <c r="E7" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F7" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.85167309644348</v>
+        <v>6.150896878172066</v>
       </c>
       <c r="D8" t="n">
-        <v>37.72479915489107</v>
+        <v>6.130279862669799</v>
       </c>
       <c r="E8" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F8" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.83023138410756</v>
+        <v>5.65991259991748</v>
       </c>
       <c r="D9" t="n">
-        <v>34.9228754338888</v>
+        <v>5.67496725800693</v>
       </c>
       <c r="E9" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F9" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.94721769126982</v>
+        <v>5.191422874831346</v>
       </c>
       <c r="D10" t="n">
-        <v>31.86994223881882</v>
+        <v>5.178865613808059</v>
       </c>
       <c r="E10" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F10" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.94554216983985</v>
+        <v>0.9661506025989757</v>
       </c>
       <c r="D11" t="n">
-        <v>6.827541750473125</v>
+        <v>1.109475534451883</v>
       </c>
       <c r="E11" t="n">
-        <v>9.097186692427762</v>
+        <v>1.478292837519511</v>
       </c>
       <c r="F11" t="n">
-        <v>8.845838099195324</v>
+        <v>1.43744869111924</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
